--- a/storage/app/templates/salary.xlsx
+++ b/storage/app/templates/salary.xlsx
@@ -406,7 +406,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="68">
+  <borders count="67">
     <border/>
     <border>
       <left/>
@@ -908,15 +908,6 @@
       <bottom/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF000000"/>
       </left>
@@ -1109,7 +1100,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="164">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1345,6 +1336,9 @@
     <xf borderId="43" fillId="0" fontId="12" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf borderId="43" fillId="0" fontId="10" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf borderId="43" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1401,11 +1395,10 @@
     <xf borderId="16" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="48" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="30" fillId="8" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="49" fillId="8" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="48" fillId="8" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -1420,7 +1413,7 @@
     <xf borderId="29" fillId="8" fontId="6" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="49" fillId="8" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="48" fillId="8" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -1447,7 +1440,7 @@
     <xf borderId="37" fillId="8" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="50" fillId="8" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="49" fillId="8" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -1456,29 +1449,29 @@
     <xf borderId="41" fillId="0" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="51" fillId="0" fontId="10" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="52" fillId="0" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="50" fillId="0" fontId="10" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="51" fillId="0" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="51" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="50" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="53" fillId="3" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="52" fillId="3" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="53" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="52" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="53" fillId="3" fontId="11" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="52" fillId="3" fontId="11" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="43" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
     <xf borderId="43" fillId="3" fontId="11" numFmtId="165" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="52" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="51" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="54" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
+    <xf borderId="53" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
@@ -1495,27 +1488,27 @@
     <xf borderId="14" fillId="8" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="55" fillId="8" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="54" fillId="8" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="55" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="30" fillId="8" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="56" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="30" fillId="8" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf borderId="57" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="58" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="8" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="29" fillId="8" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="59" fillId="8" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="58" fillId="8" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="59" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="60" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="61" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="62" fillId="8" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="61" fillId="8" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf borderId="34" fillId="8" fontId="10" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -1524,27 +1517,30 @@
     <xf borderId="37" fillId="8" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="63" fillId="8" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="62" fillId="8" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf borderId="31" fillId="8" fontId="14" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="64" fillId="8" fontId="14" numFmtId="37" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="63" fillId="8" fontId="14" numFmtId="37" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="65" fillId="0" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="64" fillId="0" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="66" fillId="0" fontId="10" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="51" fillId="0" fontId="11" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="43" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="65" fillId="0" fontId="10" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="50" fillId="0" fontId="11" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="43" fillId="0" fontId="6" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="52" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="51" fillId="0" fontId="6" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="67" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="51" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="66" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1631,7 +1627,7 @@
     <xdr:ext cx="1609725" cy="771525"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Hình ảnh"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Hình ảnh"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1664,7 +1660,7 @@
     <xdr:ext cx="1657350" cy="790575"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png" title="Hình ảnh"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Hình ảnh"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2578,30 +2574,28 @@
         <f>+G12+F12</f>
         <v>2091000</v>
       </c>
-      <c r="I12" s="83" t="str">
-        <f>#REF!</f>
-        <v>#REF!</v>
+      <c r="I12" s="83">
+        <f>'Bản chấm công trong giờ'!AI12</f>
+        <v>20</v>
       </c>
-      <c r="J12" s="82" t="str">
-        <f>ROUND(H12*$I12/$AK12,0)</f>
-        <v>#REF!</v>
+      <c r="J12" s="82">
+        <f>ROUND(H12*$I12/'Bản chấm công trong giờ'!AL12,0)</f>
+        <v>1672800</v>
       </c>
-      <c r="K12" s="82" t="str">
-        <f>ROUND((H12/$I$70)*#REF!,0)</f>
-        <v>#DIV/0!</v>
+      <c r="K12" s="82">
+        <f>ROUND((H12/'Bản chấm công trong giờ'!AL12)*'Bản chấm công trong giờ'!AJ12,0)</f>
+        <v>167280</v>
       </c>
-      <c r="L12" s="84" t="str">
-        <f>#REF!</f>
-        <v>#REF!</v>
+      <c r="L12" s="84">
+        <f>'Bản chấm công ngoài giờ'!AL12</f>
+        <v>0</v>
       </c>
-      <c r="M12" s="82" t="str">
-        <f>ROUND((H12/$I$70)*$L12,0)</f>
-        <v>#DIV/0!</v>
+      <c r="M12" s="82">
+        <f>'Bản chấm công ngoài giờ'!AL12 * 'Bản chấm công ngoài giờ'!AO12
+</f>
+        <v>0</v>
       </c>
-      <c r="N12" s="82" t="str">
-        <f>-IF(COUNTIF(#REF!,"N")&gt;1,$E12/$I$70*40%*(COUNTIF(#REF!,"N")-1),0)</f>
-        <v>#REF!</v>
-      </c>
+      <c r="N12" s="82"/>
       <c r="O12" s="85"/>
       <c r="P12" s="82" t="str">
         <f>1000000/#REF!*I12</f>
@@ -2628,9 +2622,9 @@
         <f>IF(P12&gt;730000,730000+Q12+R12,P12+Q12+R12)</f>
         <v>#REF!</v>
       </c>
-      <c r="X12" s="82" t="str">
-        <f>+IF(L12&gt;0,M12-((#REF!/8)*#REF!),0)</f>
-        <v>#REF!</v>
+      <c r="X12" s="87">
+        <f>+IF(L12&gt;0,M12-(('Bản chấm công trong giờ'!AL12)*'Bản chấm công trong giờ'!AJ12),0)</f>
+        <v>0</v>
       </c>
       <c r="Y12" s="82">
         <f>F12*$Y$10</f>
@@ -2658,7 +2652,7 @@
       </c>
       <c r="AE12" s="85"/>
       <c r="AF12" s="85"/>
-      <c r="AG12" s="87" t="str">
+      <c r="AG12" s="88" t="str">
         <f>ROUND(+$S12-$AC12-$AD12-$AB12-AE12,-2)-AF12</f>
         <v>#REF!</v>
       </c>
@@ -2670,16 +2664,16 @@
         <f>ROUND($F12*$AI$10,0)</f>
         <v>41820</v>
       </c>
-      <c r="AJ12" s="88" t="str">
+      <c r="AJ12" s="89" t="str">
         <f>+$S12+$AH12+$AI12</f>
         <v>#REF!</v>
       </c>
-      <c r="AK12" s="89"/>
-      <c r="AL12" s="90"/>
+      <c r="AK12" s="90"/>
+      <c r="AL12" s="91"/>
     </row>
     <row r="13" ht="11.25" customHeight="1">
-      <c r="A13" s="91"/>
-      <c r="B13" s="92"/>
+      <c r="A13" s="92"/>
+      <c r="B13" s="93"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
@@ -2718,8 +2712,8 @@
       <c r="AL13" s="10"/>
     </row>
     <row r="14" ht="11.25" customHeight="1">
-      <c r="A14" s="91"/>
-      <c r="B14" s="92"/>
+      <c r="A14" s="92"/>
+      <c r="B14" s="93"/>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
@@ -2758,8 +2752,8 @@
       <c r="AL14" s="10"/>
     </row>
     <row r="15" ht="11.25" customHeight="1">
-      <c r="A15" s="91"/>
-      <c r="B15" s="92"/>
+      <c r="A15" s="92"/>
+      <c r="B15" s="93"/>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
@@ -2798,8 +2792,8 @@
       <c r="AL15" s="10"/>
     </row>
     <row r="16" ht="11.25" customHeight="1">
-      <c r="A16" s="91"/>
-      <c r="B16" s="92"/>
+      <c r="A16" s="92"/>
+      <c r="B16" s="93"/>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
@@ -2838,8 +2832,8 @@
       <c r="AL16" s="10"/>
     </row>
     <row r="17" ht="11.25" customHeight="1">
-      <c r="A17" s="91"/>
-      <c r="B17" s="92"/>
+      <c r="A17" s="92"/>
+      <c r="B17" s="93"/>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
@@ -3000,7 +2994,7 @@
     <row r="21" ht="11.25" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="5"/>
-      <c r="C21" s="91"/>
+      <c r="C21" s="92"/>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
@@ -3040,7 +3034,7 @@
     <row r="22" ht="11.25" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="5"/>
-      <c r="C22" s="91"/>
+      <c r="C22" s="92"/>
       <c r="D22" s="10"/>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
@@ -3080,7 +3074,7 @@
     <row r="23" ht="11.25" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="5"/>
-      <c r="C23" s="91"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
@@ -3120,7 +3114,7 @@
     <row r="24" ht="11.25" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="5"/>
-      <c r="C24" s="91"/>
+      <c r="C24" s="92"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
@@ -11779,21 +11773,21 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="P9:R9"/>
-    <mergeCell ref="S9:S10"/>
     <mergeCell ref="AB9:AB10"/>
     <mergeCell ref="AE9:AE10"/>
+    <mergeCell ref="E8:E10"/>
     <mergeCell ref="I8:S8"/>
     <mergeCell ref="T8:Z8"/>
     <mergeCell ref="AA8:AB8"/>
     <mergeCell ref="AC8:AG8"/>
     <mergeCell ref="AH8:AJ8"/>
-    <mergeCell ref="E8:E10"/>
     <mergeCell ref="F9:H9"/>
     <mergeCell ref="I9:K9"/>
     <mergeCell ref="L9:M9"/>
     <mergeCell ref="N9:N10"/>
     <mergeCell ref="O9:O10"/>
+    <mergeCell ref="P9:R9"/>
+    <mergeCell ref="S9:S10"/>
     <mergeCell ref="T9:U9"/>
     <mergeCell ref="V9:V10"/>
     <mergeCell ref="W9:W10"/>
@@ -11879,7 +11873,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="5"/>
-      <c r="D2" s="93"/>
+      <c r="D2" s="94"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -11954,7 +11948,7 @@
       <c r="AG3" s="4"/>
       <c r="AH3" s="4"/>
       <c r="AI3" s="4"/>
-      <c r="AJ3" s="94"/>
+      <c r="AJ3" s="95"/>
       <c r="AK3" s="4"/>
       <c r="AL3" s="4"/>
       <c r="AM3" s="4"/>
@@ -11995,7 +11989,7 @@
       <c r="AG4" s="4"/>
       <c r="AH4" s="4"/>
       <c r="AI4" s="4"/>
-      <c r="AJ4" s="94"/>
+      <c r="AJ4" s="95"/>
       <c r="AK4" s="4"/>
       <c r="AL4" s="4"/>
       <c r="AM4" s="4"/>
@@ -12036,7 +12030,7 @@
       <c r="AG5" s="4"/>
       <c r="AH5" s="4"/>
       <c r="AI5" s="4"/>
-      <c r="AJ5" s="94"/>
+      <c r="AJ5" s="95"/>
       <c r="AK5" s="4"/>
       <c r="AL5" s="4"/>
       <c r="AM5" s="4"/>
@@ -12124,99 +12118,99 @@
       <c r="AM7" s="4"/>
     </row>
     <row r="8">
-      <c r="A8" s="95" t="s">
+      <c r="A8" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="96"/>
-      <c r="C8" s="96" t="s">
+      <c r="B8" s="97"/>
+      <c r="C8" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="96"/>
-      <c r="K8" s="96"/>
-      <c r="L8" s="96"/>
-      <c r="M8" s="96"/>
-      <c r="N8" s="96"/>
-      <c r="O8" s="96"/>
-      <c r="P8" s="96"/>
-      <c r="Q8" s="96"/>
-      <c r="R8" s="96"/>
-      <c r="S8" s="96"/>
-      <c r="T8" s="96"/>
-      <c r="U8" s="96"/>
-      <c r="V8" s="96"/>
-      <c r="W8" s="96"/>
-      <c r="X8" s="96"/>
-      <c r="Y8" s="96"/>
-      <c r="Z8" s="96"/>
-      <c r="AA8" s="96"/>
-      <c r="AB8" s="96"/>
-      <c r="AC8" s="96"/>
-      <c r="AD8" s="96"/>
-      <c r="AE8" s="96"/>
-      <c r="AF8" s="96"/>
-      <c r="AG8" s="96"/>
-      <c r="AH8" s="97"/>
-      <c r="AI8" s="98" t="s">
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="97"/>
+      <c r="G8" s="97"/>
+      <c r="H8" s="97"/>
+      <c r="I8" s="97"/>
+      <c r="J8" s="97"/>
+      <c r="K8" s="97"/>
+      <c r="L8" s="97"/>
+      <c r="M8" s="97"/>
+      <c r="N8" s="97"/>
+      <c r="O8" s="97"/>
+      <c r="P8" s="97"/>
+      <c r="Q8" s="97"/>
+      <c r="R8" s="97"/>
+      <c r="S8" s="97"/>
+      <c r="T8" s="97"/>
+      <c r="U8" s="97"/>
+      <c r="V8" s="97"/>
+      <c r="W8" s="97"/>
+      <c r="X8" s="97"/>
+      <c r="Y8" s="97"/>
+      <c r="Z8" s="97"/>
+      <c r="AA8" s="97"/>
+      <c r="AB8" s="97"/>
+      <c r="AC8" s="97"/>
+      <c r="AD8" s="97"/>
+      <c r="AE8" s="97"/>
+      <c r="AF8" s="97"/>
+      <c r="AG8" s="97"/>
+      <c r="AH8" s="98"/>
+      <c r="AI8" s="99" t="s">
         <v>54</v>
       </c>
-      <c r="AJ8" s="99" t="s">
+      <c r="AJ8" s="100" t="s">
         <v>55</v>
       </c>
-      <c r="AK8" s="100" t="s">
+      <c r="AK8" s="101" t="s">
         <v>27</v>
       </c>
-      <c r="AL8" s="101"/>
-      <c r="AM8" s="102"/>
+      <c r="AL8" s="102"/>
+      <c r="AM8" s="103"/>
     </row>
     <row r="9">
-      <c r="A9" s="103" t="s">
+      <c r="A9" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="104" t="s">
+      <c r="B9" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="104" t="s">
+      <c r="C9" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="104"/>
-      <c r="E9" s="104"/>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="104"/>
-      <c r="I9" s="104"/>
-      <c r="J9" s="104"/>
-      <c r="K9" s="104"/>
-      <c r="L9" s="104"/>
-      <c r="M9" s="104"/>
-      <c r="N9" s="104"/>
-      <c r="O9" s="104"/>
-      <c r="P9" s="104"/>
-      <c r="Q9" s="104"/>
-      <c r="R9" s="104"/>
-      <c r="S9" s="104"/>
-      <c r="T9" s="104"/>
-      <c r="U9" s="104"/>
-      <c r="V9" s="104"/>
-      <c r="W9" s="104"/>
-      <c r="X9" s="104"/>
-      <c r="Y9" s="104"/>
-      <c r="Z9" s="104"/>
-      <c r="AA9" s="104"/>
-      <c r="AB9" s="104"/>
-      <c r="AC9" s="104"/>
-      <c r="AD9" s="105"/>
-      <c r="AE9" s="105"/>
-      <c r="AF9" s="104"/>
-      <c r="AG9" s="106"/>
-      <c r="AH9" s="106"/>
-      <c r="AI9" s="107"/>
-      <c r="AJ9" s="107"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="105"/>
+      <c r="J9" s="105"/>
+      <c r="K9" s="105"/>
+      <c r="L9" s="105"/>
+      <c r="M9" s="105"/>
+      <c r="N9" s="105"/>
+      <c r="O9" s="105"/>
+      <c r="P9" s="105"/>
+      <c r="Q9" s="105"/>
+      <c r="R9" s="105"/>
+      <c r="S9" s="105"/>
+      <c r="T9" s="105"/>
+      <c r="U9" s="105"/>
+      <c r="V9" s="105"/>
+      <c r="W9" s="105"/>
+      <c r="X9" s="105"/>
+      <c r="Y9" s="105"/>
+      <c r="Z9" s="105"/>
+      <c r="AA9" s="105"/>
+      <c r="AB9" s="105"/>
+      <c r="AC9" s="105"/>
+      <c r="AD9" s="106"/>
+      <c r="AE9" s="106"/>
+      <c r="AF9" s="105"/>
+      <c r="AG9" s="107"/>
+      <c r="AH9" s="107"/>
+      <c r="AI9" s="36"/>
+      <c r="AJ9" s="36"/>
       <c r="AK9" s="108" t="s">
         <v>56</v>
       </c>
@@ -12226,11 +12220,11 @@
       <c r="AM9" s="110"/>
     </row>
     <row r="10">
-      <c r="A10" s="103" t="s">
+      <c r="A10" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="104"/>
-      <c r="C10" s="104"/>
+      <c r="B10" s="105"/>
+      <c r="C10" s="105"/>
       <c r="D10" s="111"/>
       <c r="E10" s="111"/>
       <c r="F10" s="111"/>
@@ -12260,8 +12254,8 @@
       <c r="AD10" s="111"/>
       <c r="AE10" s="111"/>
       <c r="AF10" s="111"/>
-      <c r="AG10" s="104"/>
-      <c r="AH10" s="104"/>
+      <c r="AG10" s="105"/>
+      <c r="AH10" s="105"/>
       <c r="AI10" s="112"/>
       <c r="AJ10" s="113"/>
       <c r="AK10" s="108" t="s">
@@ -12409,17 +12403,19 @@
       </c>
       <c r="AH12" s="131"/>
       <c r="AI12" s="132">
-        <f>COUNTIF(D12:AH12,$AB$83)+COUNTIF(D12:AH12,$AB$86)/2+COUNTIF(D12:AH12,$AB$87)+COUNTIF(D12:AH12,$AB$84)+COUNTIF(D12:AH12,$AC$88)</f>
-        <v>0</v>
+        <f>COUNTIF(D12:AH12,"x") + COUNTIF(D12:AH12,"/")*0.5 + COUNTIF(D12:AH12,"P/")*0.5</f>
+        <v>20</v>
       </c>
-      <c r="AJ12" s="133"/>
+      <c r="AJ12" s="133">
+        <f>COUNTIF(D12:AH12,"P") + COUNTIF(D12:AH12,"L") + COUNTIF(D12:AH12,"P/")*0.5</f>
+        <v>2</v>
+      </c>
       <c r="AK12" s="134">
         <f>SUM(AI12:AJ12)</f>
-        <v>0</v>
+        <v>22</v>
       </c>
-      <c r="AL12" s="135" t="str">
-        <f>+IF(LEFT(#REF!,2)="TT",#REF!-2,#REF!)</f>
-        <v>#REF!</v>
+      <c r="AL12" s="135">
+        <v>25.0</v>
       </c>
       <c r="AM12" s="136"/>
     </row>
@@ -21924,7 +21920,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="5"/>
-      <c r="D2" s="93"/>
+      <c r="D2" s="94"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -22187,51 +22183,51 @@
       <c r="AP7" s="10"/>
     </row>
     <row r="8">
-      <c r="A8" s="95" t="s">
+      <c r="A8" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="96"/>
-      <c r="C8" s="96" t="s">
+      <c r="B8" s="97"/>
+      <c r="C8" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="96"/>
-      <c r="K8" s="96"/>
-      <c r="L8" s="96"/>
-      <c r="M8" s="96"/>
-      <c r="N8" s="96"/>
-      <c r="O8" s="96"/>
-      <c r="P8" s="96"/>
-      <c r="Q8" s="96"/>
-      <c r="R8" s="96"/>
-      <c r="S8" s="96"/>
-      <c r="T8" s="96"/>
-      <c r="U8" s="96"/>
-      <c r="V8" s="96"/>
-      <c r="W8" s="96"/>
-      <c r="X8" s="96"/>
-      <c r="Y8" s="96"/>
-      <c r="Z8" s="96"/>
-      <c r="AA8" s="96"/>
-      <c r="AB8" s="96"/>
-      <c r="AC8" s="96"/>
-      <c r="AD8" s="96"/>
-      <c r="AE8" s="96"/>
-      <c r="AF8" s="96"/>
-      <c r="AG8" s="96"/>
-      <c r="AH8" s="96"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="97"/>
+      <c r="G8" s="97"/>
+      <c r="H8" s="97"/>
+      <c r="I8" s="97"/>
+      <c r="J8" s="97"/>
+      <c r="K8" s="97"/>
+      <c r="L8" s="97"/>
+      <c r="M8" s="97"/>
+      <c r="N8" s="97"/>
+      <c r="O8" s="97"/>
+      <c r="P8" s="97"/>
+      <c r="Q8" s="97"/>
+      <c r="R8" s="97"/>
+      <c r="S8" s="97"/>
+      <c r="T8" s="97"/>
+      <c r="U8" s="97"/>
+      <c r="V8" s="97"/>
+      <c r="W8" s="97"/>
+      <c r="X8" s="97"/>
+      <c r="Y8" s="97"/>
+      <c r="Z8" s="97"/>
+      <c r="AA8" s="97"/>
+      <c r="AB8" s="97"/>
+      <c r="AC8" s="97"/>
+      <c r="AD8" s="97"/>
+      <c r="AE8" s="97"/>
+      <c r="AF8" s="97"/>
+      <c r="AG8" s="97"/>
+      <c r="AH8" s="97"/>
       <c r="AI8" s="139" t="s">
         <v>54</v>
       </c>
       <c r="AJ8" s="139" t="s">
         <v>55</v>
       </c>
-      <c r="AK8" s="99" t="s">
+      <c r="AK8" s="100" t="s">
         <v>68</v>
       </c>
       <c r="AL8" s="140" t="s">
@@ -22247,49 +22243,49 @@
       <c r="AP8" s="33"/>
     </row>
     <row r="9">
-      <c r="A9" s="103" t="s">
+      <c r="A9" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="104" t="s">
+      <c r="B9" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="104" t="s">
+      <c r="C9" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="104"/>
-      <c r="E9" s="104"/>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="104"/>
-      <c r="I9" s="104"/>
-      <c r="J9" s="104"/>
-      <c r="K9" s="104"/>
-      <c r="L9" s="104"/>
-      <c r="M9" s="104"/>
-      <c r="N9" s="104"/>
-      <c r="O9" s="104"/>
-      <c r="P9" s="104"/>
-      <c r="Q9" s="104"/>
-      <c r="R9" s="104"/>
-      <c r="S9" s="104"/>
-      <c r="T9" s="104"/>
-      <c r="U9" s="104"/>
-      <c r="V9" s="104"/>
-      <c r="W9" s="104"/>
-      <c r="X9" s="104"/>
-      <c r="Y9" s="104"/>
-      <c r="Z9" s="104"/>
-      <c r="AA9" s="104"/>
-      <c r="AB9" s="104"/>
-      <c r="AC9" s="104"/>
-      <c r="AD9" s="104"/>
-      <c r="AE9" s="104"/>
-      <c r="AF9" s="104"/>
-      <c r="AG9" s="104"/>
-      <c r="AH9" s="104"/>
-      <c r="AI9" s="107"/>
-      <c r="AJ9" s="107"/>
-      <c r="AK9" s="107"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="105"/>
+      <c r="J9" s="105"/>
+      <c r="K9" s="105"/>
+      <c r="L9" s="105"/>
+      <c r="M9" s="105"/>
+      <c r="N9" s="105"/>
+      <c r="O9" s="105"/>
+      <c r="P9" s="105"/>
+      <c r="Q9" s="105"/>
+      <c r="R9" s="105"/>
+      <c r="S9" s="105"/>
+      <c r="T9" s="105"/>
+      <c r="U9" s="105"/>
+      <c r="V9" s="105"/>
+      <c r="W9" s="105"/>
+      <c r="X9" s="105"/>
+      <c r="Y9" s="105"/>
+      <c r="Z9" s="105"/>
+      <c r="AA9" s="105"/>
+      <c r="AB9" s="105"/>
+      <c r="AC9" s="105"/>
+      <c r="AD9" s="105"/>
+      <c r="AE9" s="105"/>
+      <c r="AF9" s="105"/>
+      <c r="AG9" s="105"/>
+      <c r="AH9" s="105"/>
+      <c r="AI9" s="36"/>
+      <c r="AJ9" s="36"/>
+      <c r="AK9" s="36"/>
       <c r="AL9" s="143"/>
       <c r="AM9" s="143" t="s">
         <v>70</v>
@@ -22299,11 +22295,11 @@
       <c r="AP9" s="33"/>
     </row>
     <row r="10">
-      <c r="A10" s="103" t="s">
+      <c r="A10" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="104"/>
-      <c r="C10" s="104"/>
+      <c r="B10" s="105"/>
+      <c r="C10" s="105"/>
       <c r="D10" s="111"/>
       <c r="E10" s="111"/>
       <c r="F10" s="111"/>
@@ -22457,17 +22453,23 @@
         <f>SUM(D12+E12)*3/8</f>
         <v>0</v>
       </c>
-      <c r="AL12" s="134">
+      <c r="AL12" s="161">
         <f>SUM($AI12:$AK12)</f>
         <v>0</v>
       </c>
-      <c r="AM12" s="134">
+      <c r="AM12" s="161">
         <f>+SUM($D12:$AH12)</f>
         <v>0</v>
       </c>
-      <c r="AN12" s="161"/>
-      <c r="AO12" s="162"/>
-      <c r="AP12" s="90"/>
+      <c r="AN12" s="162">
+        <f>'Bảng lương'!H12</f>
+        <v>2091000</v>
+      </c>
+      <c r="AO12" s="163">
+        <f>ROUND(AN12/'Bản chấm công trong giờ'!AL12,0)</f>
+        <v>83640</v>
+      </c>
+      <c r="AP12" s="91"/>
     </row>
     <row r="13" ht="11.25" customHeight="1">
       <c r="A13" s="10"/>
